--- a/data/memories/memory_01/assets/documents/meeting_room/Meeting Attendees.xlsx
+++ b/data/memories/memory_01/assets/documents/meeting_room/Meeting Attendees.xlsx
@@ -522,7 +522,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Laura C.</t>
+          <t>Laura L.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
